--- a/docs/02_Plan_Gestion_Riesgos.xlsx
+++ b/docs/02_Plan_Gestion_Riesgos.xlsx
@@ -157,7 +157,7 @@
     <t>Lecturas inestables del sensor de frecuencia cardiaca MAX30102 por movimiento</t>
   </si>
   <si>
-    <t>Leonardo Nágera</t>
+    <t>Leonardo Nájera</t>
   </si>
   <si>
     <t>m</t>
@@ -169,7 +169,7 @@
     <t>A: Abierto, el riesgo está latente.</t>
   </si>
   <si>
-    <t>Daño del ESP32 por mezcla de voltajes (3.3V lógica / 12V actuadores)</t>
+    <t>Daño del ESP32 por mezcla de voltajes (3.3V lógica / 12V y 5V actuadores)</t>
   </si>
   <si>
     <t>b</t>
@@ -538,10 +538,10 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>Daño del ESP32 por mezcla de voltajes (3.3V / 12V)</t>
-  </si>
-  <si>
-    <t>El ventilador y el relé operan a 12V mientras el ESP32 trabaja a 3.3V; una conexión incorrecta (sin optoacoplador o sin tierra común) puede dañar permanentemente el microcontrolador prestado por el laboratorio.</t>
+    <t>Daño del ESP32 por mezcla de voltajes (3.3V / 12V / 5V)</t>
+  </si>
+  <si>
+    <t>El ventilador (12V, regulado por el módulo D4184) y el módulo vibratorio (5V) operan a voltajes distintos al del ESP32 (3.3V); una conexión incorrecta (sin tierra común entre las fuentes y el ESP32, o sin los diodos 1N5819 de protección) puede dañar permanentemente el microcontrolador prestado por el laboratorio.</t>
   </si>
   <si>
     <t>13-oct-26</t>
@@ -571,7 +571,7 @@
     <t>Pendiente</t>
   </si>
   <si>
-    <t>Unir las tierras (GND) de la fuente de 12V y el ESP32 antes de probar</t>
+    <t>Unir las tierras (GND) de las fuentes de 12V y 5V y el ESP32 antes de probar</t>
   </si>
   <si>
     <t>Aunque el sprint de construcción es de solo 14 días, un retraso acumulado en tareas de la ruta crítica o imprevistos no resueltos durante las 6 semanas de margen podrían impedir tener el prototipo listo para la demostración final.</t>

--- a/docs/02_Plan_Gestion_Riesgos.xlsx
+++ b/docs/02_Plan_Gestion_Riesgos.xlsx
@@ -292,7 +292,7 @@
     <t>B: Bajo.</t>
   </si>
   <si>
-    <t>Caída del servicio externo de IA (API tipo ChatGPT) el día de la demostración</t>
+    <t>Modelo de IA entrenado ausente o corrupto el día de la demostración</t>
   </si>
   <si>
     <t>a 12</t>
@@ -514,7 +514,7 @@
     <t>Completado</t>
   </si>
   <si>
-    <t>Tener como respaldo el STCC4 (SEN0678) o MH-Z19B + AM2302</t>
+    <t>Tener como respaldo el STCC4 (SEN0678) o MH-Z19B (el AM2302 ya no forma parte del proyecto)</t>
   </si>
   <si>
     <t>En espera</t>
@@ -694,19 +694,19 @@
     <t>Nota: la seguridad de las personas va primero. Ningún entregable justifica un riesgo físico real; ante un imprevisto grave, se avisa al profesor de inmediato.</t>
   </si>
   <si>
-    <t>Caída del servicio externo de IA (API tipo ChatGPT) el día de la demo</t>
-  </si>
-  <si>
-    <t>Si el módulo de IA depende de una API externa para generar explicaciones o resúmenes, una caída de ese servicio justo el día de la demostración dejaría esa función sin responder, aunque el resto del sistema (sensores, base de datos, ventilador) siga funcionando con normalidad.</t>
-  </si>
-  <si>
-    <t>Módulo de IA (parte conversacional)</t>
+    <t>Modelo de IA entrenado ausente o corrupto el día de la demo</t>
+  </si>
+  <si>
+    <t>El sistema de IA es 100% local (scikit-learn) y no usa ninguna API externa. El modelo (co2_model.joblib) se genera con python ia/train.py y no se guarda en el repositorio; si falta o se corrompe en la Raspberry Pi, el módulo pierde la recomendación basada en el modelo y solo opera la regla de pendiente, aunque el resto del sistema (sensores, base de datos, ventilador) siga funcionando con normalidad.</t>
+  </si>
+  <si>
+    <t>Módulo de IA (recomendación del modelo)</t>
   </si>
   <si>
     <t>Percepción general de la demostración</t>
   </si>
   <si>
-    <t>La función de explicación por IA no responde en vivo</t>
+    <t>La recomendación de ventilación anticipada del modelo no se aplica en vivo</t>
   </si>
   <si>
     <t>Posible impresión de que el sistema completo falla, aunque el resto sí opere</t>
@@ -715,13 +715,13 @@
     <t>Interrupción del flujo de la presentación</t>
   </si>
   <si>
-    <t>Guardar en caché la última respuesta exitosa de la IA para mostrarla si el servicio falla</t>
+    <t>Guardar una copia de respaldo del archivo co2_model.joblib fuera de la Raspberry Pi</t>
   </si>
   <si>
     <t>Explicar en la presentación qué partes del sistema no dependen de internet</t>
   </si>
   <si>
-    <t>Probar la conexión a la API la noche y la mañana antes de la entrega</t>
+    <t>Verificar que ia/models/co2_model.joblib existe y carga sin error la noche y la mañana antes de la entrega</t>
   </si>
   <si>
     <t>02 y 03-dic-26</t>
